--- a/Result/profitability/3629.xlsx
+++ b/Result/profitability/3629.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.16</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.008750000000000008</v>
+        <v>0.01124999999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>47.35625</v>
+        <v>44.05375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06874999999999999</v>
+        <v>0.08249999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>41.99625</v>
+        <v>40.95125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-1.1</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.04500000000000001</v>
+        <v>-0.02625000000000002</v>
       </c>
       <c r="N4" t="n">
-        <v>37.1225</v>
+        <v>32.605</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.27</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.05000000000000002</v>
+        <v>-0.02375000000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>28.41875</v>
+        <v>22.7875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.87</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09499999999999997</v>
+        <v>0.1125</v>
       </c>
       <c r="N6" t="n">
-        <v>22.76125</v>
+        <v>21.34375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.52</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1875</v>
+        <v>0.16625</v>
       </c>
       <c r="N7" t="n">
-        <v>20.02875</v>
+        <v>22.18875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.42</v>
       </c>
       <c r="M8" t="n">
-        <v>0.22875</v>
+        <v>0.2375</v>
       </c>
       <c r="N8" t="n">
-        <v>20.6075</v>
+        <v>21.58125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9669,6 +9669,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3629</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>13</v>
+      </c>
+      <c r="D74" t="n">
+        <v>8</v>
+      </c>
+      <c r="E74" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-23.15%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>-3</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="M74" t="n">
+        <v>-0.16375</v>
+      </c>
+      <c r="N74" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0.06999999999999999</v>
+      </c>
+      <c r="X74" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>7.789999999999999</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.2753623188405796</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>-0.7241379310344827</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>-45.05</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>-0.5552816467398003</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
